--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_12_Full_159_Cau/Day_12_Ngan_Hang_Phan_02_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_12_Full_159_Cau/Day_12_Ngan_Hang_Phan_02_20_Cau.xlsx
@@ -675,7 +675,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xác định path cần ghi và user sở hữu nó trước khi chuyển sang `USER`.</t>
+          <t>Để tiến trình chạy dưới user non-root (`USER 10001`) có thể ghi vào thư mục `/app/tmp`, Dockerfile cần gán quyền sở hữu hoặc quyền ghi tối thiểu cho thư mục đó trước khi chuyển sang lệnh `USER`.</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt file bị Git bỏ qua với file Docker vẫn gửi trong build context.</t>
+          <t>Docker build context gửi tất cả các tệp trong thư mục trừ khi được chỉ định rõ trong `.dockerignore`; tệp `.gitignore` không có tác dụng với Docker daemon khi build image.</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xác định finding nằm trong final image nào, package còn reachable lúc chạy không và bằng chứng còn hiệu lực đến khi nào.</t>
+          <t>Để quyết định phát hành D1 khi builder stage có CVE: Cần (a) image digest bất biến D1 đã qua quét, (b) SBOM của final image để chứng minh package lỗi không tồn tại hoặc không reachable ở runtime, (c) đánh giá mức độ, bản vá và exception owner có thời hạn.</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Trong Compose hãy gọi tên service; readiness là khả năng phục vụ, không chỉ process đã start.</t>
+          <t>Trong Docker Compose, các service độc lập giao tiếp qua mạng nội bộ bằng tên service DNS và cần khai báo điều kiện phụ thuộc trạng thái sẵn sàng (healthcheck/readiness), không gọi `localhost`.</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu thời lượng tác vụ với timeout, rồi kiểm tra cách lấy kết quả sau khi submit.</t>
+          <t>Khi tác vụ xử lý kéo dài 90s vượt quá thời gian timeout 30s của HTTP gateway, giải pháp kiến trúc chuẩn là chuyển sang mô hình Async Job (HTTP 202 Accepted) kèm `job_id` và endpoint tra cứu trạng thái/kết quả.</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt first-byte latency với tổng compute.</t>
+          <t>Server-Sent Events (SSE) streaming giúp giảm độ trễ của token đầu tiên (Time-to-First-Token - TTFT) để cải thiện trải nghiệm người dùng, nhưng không làm giảm tổng khối lượng tính toán của mô hình.</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tìm ranh giới intermediary: byte có được đẩy ra sớm, connection có được giữ sống và event có thể resume không.</t>
+          <t>Khi streaming SSE bị proxy gom buffer, giải pháp vận hành là tắt cơ chế buffering trên reverse proxy (`proxy_buffering off`), ép flush sớm và bổ sung heartbeat/event ID để duy trì kết nối.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_12_Full_159_Cau/Day_12_Ngan_Hang_Phan_02_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_12_Full_159_Cau/Day_12_Ngan_Hang_Phan_02_20_Cau.xlsx
@@ -624,10 +624,37 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách build artifact trước, rồi kiểm tra chính final image có đủ thư viện để khởi động.
-Phân tích theo nguyên lý thiết kế: Tách build artifact trước, rồi kiểm tra chính final image có đủ thư viện để khởi động.</t>
+- [1.5 điểm] Thiết kế đầy đủ 2 stage rõ ràng: Builder stage biên dịch wheel và Runtime stage tối thiểu hóa copy artifacts.
+- [1.5 điểm] Xử lý chính xác việc cài đặt runtime shared libraries ở stage cuối để ngăn chặn crash runtime.
+- [1.0 điểm] Thiết lập phương pháp xác minh filesystem: kiểm tra loại bỏ build tools (gcc) và xác nhận liên kết thư viện bằng ldd.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Dockerfile Đa giai đoạn (Multi-stage Build Architecture):
+```dockerfile
+# STAGE 1: Build &amp; Compile Stage (Chứa đầy đủ compiler và build tools)
+FROM python:3.11-slim AS builder
+WORKDIR /build
+RUN apt-get update &amp;&amp; apt-get install -y --no-install-recommends gcc g++ build-essential libpq-dev
+COPY requirements.txt .
+RUN pip wheel --no-cache-dir --wheel-dir=/build/wheels -r requirements.txt
+# STAGE 2: Final Minimal Runtime Stage (Siêu nhẹ, loại bỏ compiler)
+FROM python:3.11-slim AS runtime
+WORKDIR /app
+# BẮT BUỘC: Cài đặt runtime shared libraries (không cài build tools)
+RUN apt-get update &amp;&amp; apt-get install -y --no-install-recommends libpq5 &amp;&amp; rm -rf /var/lib/apt/lists/*
+# Copy wheels từ builder stage và cài đặt
+COPY --from=builder /build/wheels /wheels
+RUN pip install --no-cache-dir --no-index --find-links=/wheels /wheels/* &amp;&amp; rm -rf /wheels
+COPY app/ ./app/
+USER 10001:10001
+CMD ["python", "-m", "app.main"]
+```
+2. Xác minh Filesystem và Shared Library ở Final Image:
+   - Kiểm tra loại trừ Build Tools: `docker run --rm runtime which gcc` -&gt; Phải trả về mã lỗi (exit code 1, không tìm thấy gcc), đảm bảo bề mặt tấn công tối thiểu.
+   - Kiểm tra liên kết Thư viện Động (Dynamic Shared Library Linkage Verification): Chạy công cụ kiểm tra phụ thuộc thư viện native của Python extension: `docker run --rm runtime ldd /usr/local/lib/python3.11/site-packages/.../*.so`. Xác nhận 100% các file `.so` đều tìm thấy thư viện chia sẻ liên kết (không có thông báo `not found`), chứng minh container không bị crash khi chạy tác vụ thực tế.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Multi-stage build cho phép phân tách rạch ròi giữa 'Môi trường Xây dựng' (chứa trình biên dịch nặng nề như gcc, g++) và 'Môi trường Thực thi' (chỉ chứa tệp thực thi sạch và thư viện runtime tối thiểu). Tuy nhiên, cạm bẫy lớn nhất là thiếu các shared dynamic libraries (như `libpq.so.5` cho PostgreSQL) ở stage cuối dẫn đến crash khi khởi động. Việc cài đặt đúng gói runtime shared library và kiểm tra bằng lệnh `ldd` là tiêu chuẩn vàng của containerization an toàn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Docker Documentation - Multi-stage builds: https://docs.docker.com/build/building/multi-stage/ và Debian Packages Runtime Libraries</t>
         </is>
       </c>
     </row>
@@ -706,10 +733,33 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Phân biệt quyền cần cấp cho `/data/jobs` với thao tác phải bị từ chối ở path đặc quyền.
-Phân tích theo nguyên lý thiết kế: Phân biệt quyền cần cấp cho `/data/jobs` với thao tác phải bị từ chối ở path đặc quyền.</t>
+- [1.0 điểm] Cấu hình runtime non-root hoàn chỉnh: USER UID 10001, chown riêng `/data/jobs`, read-only rootfs và cap_drop ALL.
+- [1.5 điểm] Thiết kế bộ negative test matrix chi tiết chứng minh bị từ chối khi ghi `/etc`, bind port &lt; 1024 và cài package.
+- [1.5 điểm] Kiểm thử positive test xác nhận ghi file thành công tại `/data/jobs` và kích hoạt cờ no-new-privileges.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Runtime Container Non-Root và Phân quyền Tối thiểu:
+   - Cấu hình Dockerfile với User không đặc quyền:
+     ```dockerfile
+     RUN groupadd -g 10001 appgroup &amp;&amp; \
+         useradd -u 10001 -g appgroup -s /sbin/nologin -M appuser &amp;&amp; \
+         mkdir -p /data/jobs &amp;&amp; \
+         chown -R 10001:10001 /data/jobs &amp;&amp; \
+         chmod 700 /data/jobs
+     USER 10001:10001
+     ```
+   - Ràng buộc Runtime Security Context (Docker/Kubernetes):
+     + `read_only_root_filesystem: true` (Toàn bộ root filesystem chỉ đọc, ngoại trừ volume mount `/data/jobs`).
+     + `drop_capabilities: ["ALL"]` (Tước bỏ toàn bộ đặc quyền Linux capabilities như `CAP_NET_BIND_SERVICE`, `CAP_SYS_ADMIN`).
+     + `no_new_privileges: true` (Ngăn chặn tiến trình nâng quyền thông qua setuid binaries).
+2. Thiết kế Bộ kiểm thử các Thao tác Phải bị Từ chối (Negative Test Matrix):
+   - Test 1 (Ghi vào thư mục hệ thống): Thực thi lệnh `touch /etc/hacked.txt` hoặc `touch /usr/local/bin/test` -&gt; Kết quả mong đợi: Bị từ chối với lỗi `Read-only file system` hoặc `Permission denied` (EACCES).
+   - Test 2 (Bind cổng đặc quyền mạng &lt; 1024): Cho agent chạy socket listener trên port 80 hoặc 443 -&gt; Kết quả mong đợi: Lập tức bị từ chối với lỗi `Permission denied` do thiếu `CAP_NET_BIND_SERVICE`.
+   - Test 3 (Cài đặt package hệ điều hành): Chạy `apt-get install -y curl` hoặc `su / sudo` -&gt; Kết quả mong đợi: Lỗi `Permission denied: Are you root?` hoặc command không tồn tại.
+   - Test 4 (Positive Test - Ghi hợp lệ vào `/data/jobs`): Chạy lệnh `echo '{"job_id": "1"}' &gt; /data/jobs/job_1.json` -&gt; Kết quả mong đợi: Ghi thành công hoàn toàn với quyền sở hữu `appuser:appgroup`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Đặc quyền Tối thiểu (Principle of Least Privilege) trong bảo mật container yêu cầu cô lập triệt để tiến trình ứng dụng khỏi root host. Bằng cách gán non-root UID 10001, tước bỏ toàn bộ Linux capabilities và khóa rootfs ở chế độ Read-Only, hệ thống triệt tiêu nguy cơ container breakout ngay cả khi mã nguồn của Agent có lỗ hổng thực thi mã từ xa (RCE).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+CIS Docker Benchmark v1.6.0 &amp; Kubernetes Security Context Best Practices: https://kubernetes.io/docs/tasks/configure-pod-container/security-context/</t>
         </is>
       </c>
     </row>
@@ -788,10 +838,39 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi rule phải trả lời hai việc: secret không vào context và migration vẫn vào final image.
-Phân tích theo nguyên lý thiết kế: Mỗi rule phải trả lời hai việc: secret không vào context và migration vẫn vào final image.</t>
+- [1.0 điểm] Phân tích chính xác xung đột loại trừ của rule `**/*.sql` và sửa `.dockerignore` với cú pháp phủ định `!app/migrations/*.sql`.
+- [1.5 điểm] Thiết lập ranh giới loại trừ toàn diện chặn triệt để secret (.env, .pem, .key, dumps) không lọt vào context.
+- [1.5 điểm] Xây dựng bộ kiểm tra Docker run/find và layer history chứng minh migration có mặt còn secret vắng bóng 100%.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân tích Xung đột và Thiết kế Boundary Loại trừ trong `.dockerignore`:
+   - Vấn đề: Rule `**/*.sql` loại trừ mù quáng tất cả các file SQL, khiến thư mục `app/migrations/*.sql` cần cho quá trình khởi tạo lược đồ cơ sở dữ liệu runtime bị thiếu hụt.
+   - Thiết kế quy tắc `.dockerignore` kết hợp phủ định (Negation Pattern `!`):
+     ```dockerignore
+     # 1. Loại bỏ các file nhạy cảm và secret môi trường
+     **/.env*
+     **/*.pem
+     **/*.key
+     **/*.crt
+     **/*.dump
+     dumps/
+     # 2. Loại bỏ các file SQL tùy tiện hoặc database backups ngoài ý muốn
+     **/*.sql
+     # 3. Ngoại lệ rõ ràng cho các file migration bắt buộc của runtime
+     !app/migrations/*.sql
+     !app/migrations/**/*.sql
+     ```
+2. Thiết kế Bộ kiểm thử Image Verification:
+   - Test 1 (Positive Verification - File bắt buộc hiện diện):
+     Chạy lệnh `docker run --rm &lt;built_image&gt; ls -la /app/migrations` -&gt; Kiểm tra exit code = 0 và danh sách tệp hiển thị đầy đủ các file như `001_initial_schema.sql`.
+   - Test 2 (Negative Verification - Secret và SQL rác hoàn toàn vắng mặt):
+     Chạy lệnh `docker run --rm &lt;built_image&gt; find / -name '*.env*' -o -name '*.key' -o -name '*.pem'` -&gt; Kỳ vọng trả về danh sách rỗng (0 matches).
+     Chạy lệnh `docker run --rm &lt;built_image&gt; find / -path '/app/migrations' -prune -o -name '*.sql' -print` -&gt; Xác nhận không có bất kỳ file SQL nào ngoài thư mục migrations lọt vào image.
+   - Test 3 (Layer History Inspection):
+     Chạy `docker history --no-trunc &lt;built_image&gt;` -&gt; Kiểm tra các lệnh COPY để chắc chắn không có layer nào vô tình copy secret vào rồi xóa ở layer sau.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+File `.dockerignore` là ranh giới phòng thủ đầu tiên ngăn chặn rò rỉ bí mật vào Docker Build Context. Cú pháp phủ định `!` cho phép tạo ra quy tắc loại trừ có chọn lọc (Selective Whitelisting): Chặn toàn bộ file SQL nguy hiểm (như database dumps, test queries) nhưng giữ lại các file migration cốt lõi trong đường dẫn xác định, đảm bảo tính toàn vẹn của ứng dụng khi triển khai.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Docker Documentation - .dockerignore file: https://docs.docker.com/build/building/context/#dockerignore-files và OWASP Docker Security Cheat Sheet</t>
         </is>
       </c>
     </row>
@@ -876,10 +955,26 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Ngoại lệ chỉ có hiệu lực trong thời hạn đã ghi; khóa identity bằng digest và đặt mốc scan lại.
-Phân tích theo nguyên lý thiết kế: Ngoại lệ chỉ có hiệu lực trong thời hạn đã ghi; khóa identity bằng digest và đặt mốc scan lại.</t>
+- [1.0 điểm] Đưa ra quyết định phát hành có điều kiện chặt chẽ kèm biện pháp giảm thiểu bù đắp (Compensating Controls) trong 48h.
+- [1.5 điểm] Lưu giữ đầy đủ bằng chứng kiểm toán: Immutable Image Digest sha256, vé ngoại lệ có chữ ký CISO/PO và báo cáo scan CVE.
+- [1.5 điểm] Thiết lập lịch kiểm tra lại tự động tại mốc T+48h (thu hồi ngoại lệ) và mốc T+5 ngày (triển khai bản vá D3 mới).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Quyết định Phát hành có Điều kiện (Conditional Release Governance Decision):
+   - Không cấp ngoại lệ vô điều kiện. Phê duyệt Ngoại lệ Bảo mật có Giới hạn Thời gian (Time-boxed Security Exception) tối đa 48 giờ đối với Digest D2, với điều kiện bắt buộc phải triển khai Biện pháp Giảm thiểu Bù đắp (Compensating Controls):
+     + Cách ly mạng (Egress/Ingress Isolation): Chặn đường tấn công trực tiếp tới module dính High CVE tại tầng WAF/API Gateway bằng quy tắc regex/payload filter.
+     + Giới hạn môi trường: Chỉ phát hành canary hoặc giới hạn lưu lượng, cấm mở rộng quy mô public toàn phần.
+   - Nếu không có compensating control khả thi nào để ngăn chặn khả năng khai thác của CVE reachable này: Quyết định dứt khoát là CHẶN PHÁT HÀNH (REJECT RELEASE).
+2. Bằng chứng Kiểm toán Bắt buộc Cần Lưu giữ (Audit Evidence Trail):
+   - Khóa danh tính bất biến bằng Image Digest: Ghi nhận chính xác `image@sha256:D2...` (không chấp nhận mutable tag như `:latest`).
+   - Hồ sơ Ngoại lệ Bảo mật (Security Exception Ticket): Lưu trữ chữ ký phê duyệt đồng thuận từ Security Lead / CISO và Business Product Owner, đính kèm báo cáo đánh giá rủi ro (Risk Assessment) và mô tả chi tiết compensating controls.
+   - Báo cáo Quét lỗ hổng (Vulnerability Scan Report): File xuất JSON từ scanner (Trivy/Grype) lưu trữ CVE ID, CVSS v3 score, vector khai thác và phân tích khả năng tiếp cận (Reachability Proof).
+3. Lịch Kiểm tra lại và Cơ chế Thu hồi Tự động (Re-check &amp; Revocation Schedule):
+   - Mốc T+48 Giờ: Policy Controller (như Kyverno hoặc OPA Gatekeeper) tự động kích hoạt hết hạn ngoại lệ (Exception Expiration). Nếu image D2 chưa được thay thế, admission controller lập tức chặn restart pod và gửi cảnh báo đỏ P1.
+   - Mốc T+5 Ngày: Kích hoạt pipeline build tự động kéo bản vá upstream, tạo Image Digest D3 mới, chạy quét sạch CVE và thực hiện rolling update thay thế hoàn toàn D2.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Quản trị ngoại lệ bảo mật (Vulnerability Exception Governance) trong quy trình CI/CD là cầu nối giữa rủi ro an ninh và nhu cầu kinh doanh. Khóa cứng bằng Immutable Digest bảo đảm ngoại lệ chỉ áp dụng cho đúng mã nhị phân cụ thể đó mà không bị trôi tag. Cơ chế hết hạn tự động (Time-boxed TTL) ngăn ngừa việc ngoại lệ tạm thời biến thành lỗ hổng vĩnh viễn bị lãng quên trong môi trường production.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+NIST SP 800-190 (Application Container Security Guide) &amp; CNCF Software Supply Chain Best Practices</t>
         </is>
       </c>
     </row>
@@ -958,10 +1053,58 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Theo dõi ba ranh giới: service discovery, readiness và state persistence.
-Phân tích theo nguyên lý thiết kế: Theo dõi ba ranh giới: service discovery, readiness và state persistence.</t>
+- [1.0 điểm] Sửa Compose contract chính xác: cấu hình Redis persistent volume và Agent deploy scale replicas = 3.
+- [1.5 điểm] Thiết lập cơ chế Deep Readiness Healthcheck cho Agent và dependency condition `service_healthy`.
+- [1.5 điểm] Trình bày phương pháp xác minh toàn diện: kiểm thử session sống qua container restart và proxy zero-downtime routing.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Sửa Contract Docker Compose (`docker-compose.yml`):
+   ```yaml
+   version: '3.8'
+   services:
+     redis:
+       image: redis:7-alpine
+       command: ["redis-server", "--appendonly", "yes"]
+       volumes:
+         - redis_data:/data
+       healthcheck:
+         test: ["CMD", "redis-cli", "ping"]
+         interval: 5s
+         timeout: 3s
+         retries: 3
+     agent:
+       image: enterprise-agent:v1.2
+       deploy:
+         replicas: 3
+       environment:
+         - REDIS_URL=redis://redis:6379/0
+       depends_on:
+         redis:
+           condition: service_healthy
+       healthcheck:
+         test: ["CMD", "curl", "-f", "http://localhost:8000/health/readiness"]
+         interval: 5s
+         timeout: 3s
+         retries: 3
+         start_period: 10s
+     proxy:
+       image: nginx:alpine
+       ports:
+         - "80:80"
+       depends_on:
+         - agent
+   volumes:
+     redis_data:
+   ```
+2. Cấu hình Proxy Định tuyến theo Readiness và Service Discovery:
+   - Cấu hình Nginx/Traefik upstream trỏ tới DNS `agent:8000` (Docker DNS tự động cân bằng tải giữa các container có IP khỏe mạnh).
+   - Thiết lập proxy chỉ forward traffic tới các replica có trạng thái `healthy` (HTTP 200 từ `/health/readiness`).
+3. Phương pháp Xác minh Thực tế:
+   - Xác minh 1 (Session Persistence Test): Gửi request tạo session trên container Agent-1 (ghi session data vào Redis). Chạy `docker compose stop agent_1` để hủy container; gửi request tiếp theo qua proxy, proxy tự động chuyển sang Agent-2 hoặc Agent-3; kiểm tra session vẫn tồn tại nguyên vẹn.
+   - Xác minh 2 (Zero-Downtime Readiness Test): Trong quá trình khởi động lại từng replica (rolling update), liên tục bắn HTTP requests; quan sát proxy log để xác nhận 100% request đều trả về HTTP 200, không có bất kỳ phản hồi 502 Bad Gateway nào do proxy không định tuyến tới container chưa ready.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Kiến trúc Stateless Agent với Redis Persistent Storage tuân thủ nguyên tắc Factor VI (Stateless Processes) và Factor IX (Disposability) của 12-Factor App. Bằng việc phân tách trạng thái phiên ra Redis volume và kết hợp điều kiện `service_healthy` cùng Deep Readiness Probe, hệ thống bảo đảm khả năng co giãn ngang (horizontal scaling) lên 3 replica mà không bao giờ làm gián đoạn trải nghiệm người dùng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Docker Compose File Specification: https://docs.docker.com/compose/compose-file/ và NGINX Reverse Proxy Health Checks Guide</t>
         </is>
       </c>
     </row>
@@ -1040,10 +1183,28 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách ba mốc: token đầu tiên, lúc stream kết thúc và hành vi khi client disconnect.
-Phân tích theo nguyên lý thiết kế: Tách ba mốc: token đầu tiên, lúc stream kết thúc và hành vi khi client disconnect.</t>
+- [1.0 điểm] Lựa chọn chính xác mô hình Server-Sent Events (SSE) và giải thích ưu thế so với WebSocket cho chat streaming.
+- [1.5 điểm] Mô tả chính xác hành vi tại TTFT 300ms (flush socket, disable proxy buffer) và khi hoàn tất 20s (event done, usage metadata).
+- [1.5 điểm] Thiết kế quy trình xử lý ngắt kết nối phía client: phát hiện disconnect, abort upstream LLM để tiết kiệm chi phí và ghi log.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn Mô hình Vòng đời Giao tiếp (Lifecycle Model):
+   - Lựa chọn Server-Sent Events (SSE) trên nền HTTP Streaming (MIME type: `text/event-stream`).
+   - Biện minh: Chat completion là luồng dữ liệu đơn hướng (Unidirectional Stream) từ máy chủ về máy khách sau yêu cầu POST khởi tạo. SSE nhẹ hơn, dễ cấu hình qua proxy/WAF hơn WebSocket (không cần nâng cấp protocol phức tạp), hỗ trợ native reconnection và xử lý backpressure hiệu quả.
+2. Mô tả Hành vi Chi tiết ở Các Cột mốc Vòng đời:
+   - Mốc 1 (First Token Latency - 300ms):
+     + Máy chủ gửi ngay HTTP status 200 với các headers: `Content-Type: text/event-stream`, `Cache-Control: no-cache`, `Connection: keep-alive`, `X-Accel-Buffering: no` (vô hiệu hóa proxy buffer).
+     + Đẩy ngay chunk đầu tiên: `event: delta\ndata: {"token": "Xin"}\n\n` và flush socket ngay lập tức để client hiển thị từ đầu tiên trong vòng 300ms.
+   - Mốc 2 (Hoàn tất thành công - 20s):
+     + Khi LLM kết thúc sinh dữ liệu, máy chủ phát sự kiện hoàn tất chuẩn: `event: done\ndata: {"finish_reason": "stop", "total_tokens": 512, "duration_ms": 20000}\n\n`.
+     + Máy chủ đóng HTTP stream một cách duyên dáng (Graceful TCP Close) và ghi log kiểm toán giao dịch thành công.
+   - Mốc 3 (Client Chủ động Ngắt Kết nối - Disconnect Handling):
+     + Lắng nghe sự kiện ngắt kết nối socket (FastAPI/ASGI `request.is_disconnected()` hoặc asyncio `CancelledError`).
+     + Hành vi dứt khoát: Ngay lập tức gửi tín hiệu hủy (Abort Signal) tới Model Provider API để dừng việc sinh token tiếp theo, tránh lãng phí chi phí token downstream.
+     + Hủy bỏ các tác vụ nền liên quan và ghi log trạng thái `status: client_aborted` kèm số lượng token đã tiêu thụ thực tế.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Xử lý vòng đời HTTP Streaming cho AI Agent đòi hỏi sự phối hợp chặt chẽ giữa giảm thiểu độ trễ phản hồi ban đầu (Time-to-First-Token) và quản lý tài nguyên khi xảy ra ngắt kết nối đột ngột. Việc lắng nghe tín hiệu client disconnect để hủy cuộc gọi model ngược dòng (Upstream Abort) là biện pháp then chốt giúp doanh nghiệp ngăn chặn rò rỉ ngân sách GPU/API.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+W3C Server-Sent Events Specification: https://html.spec.whatwg.org/multipage/server-sent-events.html và OpenAI Streaming API Best Practices</t>
         </is>
       </c>
     </row>
@@ -1126,10 +1287,40 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đếm terminal event và kiểm thứ tự A→B trước khi kiểm completion/usage.
-Phân tích theo nguyên lý thiết kế: Đếm terminal event và kiểm thứ tự A→B trước khi kiểm completion/usage.</t>
+- [1.0 điểm] Thiết kế định dạng chuỗi sự kiện SSE chuẩn xác với 2 chunks A, B và terminal completion event kèm usage tokens.
+- [1.5 điểm] Xây dựng bộ kiểm tra thứ tự tuần tự A -&gt; B nghiêm ngặt và kiểm tra phân tách ranh giới các block sự kiện.
+- [1.5 điểm] Kiểm tra tính duy nhất của terminal event, tính toàn vẹn của usage metadata và ký hiệu đóng stream chuẩn [DONE].
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Chuỗi Sự kiện SSE Chuẩn Hóa (Standard SSE Event Sequence):
+   ```http
+   HTTP/1.1 200 OK
+   Content-Type: text/event-stream
+   Cache-Control: no-cache
+   Connection: keep-alive
+   event: message
+   id: evt-001
+   data: {"type": "content_delta", "index": 0, "text": "A"}
+   event: message
+   id: evt-002
+   data: {"type": "content_delta", "index": 1, "text": "B"}
+   event: completion
+   id: evt-003
+   data: {"type": "message_stop", "finish_reason": "end_turn", "usage": {"input_tokens": 25, "output_tokens": 2, "total_tokens": 27}}
+   data: [DONE]
+   ```
+2. Thiết kế Bộ kiểm tra Toàn vẹn Chuỗi Sự kiện (Event Stream Test Suite):
+   - Test 1 (Thứ tự Tuần tự Nghiêm ngặt - Strict Ordering Test):
+     Đọc stream bằng SSE client parser; ghi nhận mảng các event nhận được. Khẳng định `received[0].data['text'] == 'A'` và `received[1].data['text'] == 'B'`. Nếu nhận B trước A thì đánh fail test.
+   - Test 2 (Đếm và Xác thực Terminal Event - Terminal Event Assertion):
+     Khẳng định sự kiện `completion` xuất hiện đúng 1 lần duy nhất trong toàn bộ vòng đời stream và luôn nằm sau tất cả các `content_delta` events.
+   - Test 3 (Cấu trúc Usage Metadata Test):
+     Phân tích JSON của event `completion`; xác nhận các trường `input_tokens`, `output_tokens`, `total_tokens` là số nguyên dương và thỏa mãn `input_tokens + output_tokens == total_tokens`.
+   - Test 4 (Stream Terminator Test):
+     Kiểm tra dòng đóng stream cuối cùng `data: [DONE]` trước khi kết nối TCP đóng hoàn toàn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Thiết kế giao thức truyền phát sự kiện cho LLM đòi hỏi tính cấu trúc cao. Việc phân định rõ ràng giữa các sự kiện nội dung trung gian (`message`/`content_delta`) và sự kiện kết thúc duy nhất (`completion`) kèm siêu dữ liệu sử dụng token (`usage`) giúp client vừa hiển thị giao diện mượt mà theo thời gian thực vừa cập nhật chính xác hạn ngạch chi phí của người dùng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic Messages Streaming Protocol: https://docs.anthropic.com/en/api/messages-streaming và IETF SSE Specifications</t>
         </is>
       </c>
     </row>
@@ -1256,10 +1447,29 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đầu tiên giữ connection sống dưới 60 giây, sau đó dùng ID để resume đúng điểm mà không phát trùng.
-Phân tích theo nguyên lý thiết kế: Đầu tiên giữ connection sống dưới 60 giây, sau đó dùng ID để resume đúng điểm mà không phát trùng.</t>
+- [1.0 điểm] Phân tích nguyên nhân proxy timeout 60s và thiết kế cơ chế Heartbeat ping định kỳ 15s bằng SSE comment `: ping`.
+- [1.5 điểm] Thiết kế gán Monotonic Event ID tăng dần và kiến trúc Ring Buffer lưu trữ sự kiện phía máy chủ.
+- [1.5 điểm] Xây dựng logic xử lý header Last-Event-ID khi client reconnect, đảm bảo chỉ phát bù event thiếu và chống trùng lặp.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Cơ chế Giữ Kết nối Sống Vượt qua Proxy Idle Timeout 60s:
+   - Phân tích: Proxy ngắt kết nối nếu không có byte nào được truyền trong 60 giây. Khoảng im lặng 70 giây giữa các chunk chắc chắn gây ra lỗi 504 Gateway Timeout.
+   - Thiết kế Heartbeat / Ping định kỳ:
+     + Máy chủ khởi tạo một background timer gửi SSE comment định kỳ mỗi 15 giây (&lt; 60s): `: ping\n\n`.
+     + Theo đặc tả SSE, các dòng bắt đầu bằng dấu hai chấm `:` là comment và bị client bỏ qua, không ảnh hưởng đến dữ liệu hiển thị nhưng giữ cho kết nối TCP/HTTP luôn có lưu lượng, ngăn chặn reverse proxy đóng kết nối.
+2. Thiết kế Cơ chế Resume và Reconnect Không Trùng Sự kiện:
+   - Gán ID Đơn điệu (Monotonic Event IDs) phía Máy chủ:
+     + Mỗi chunk dữ liệu gửi đi được gắn kèm một ID duy nhất tăng dần: `id: evt_001`, `id: evt_002`, ...
+     + Máy chủ duy trì một bộ đệm vòng (Ring Buffer trong Redis hoặc In-memory Cache) lưu trữ các event đã phát của stream trong vòng 10 phút, lập chỉ mục theo Event ID.
+   - Cơ chế Reconnect với `Last-Event-ID` phía Máy khách:
+     + Trình duyệt/Client tự động lưu `Last-Event-ID` của event gần nhất nhận được. Khi kết nối bị đứt, client gửi lại HTTP GET kèm header `Last-Event-ID: evt_001`.
+   - Xử lý Resume phía Máy chủ:
+     + Khi nhận request có `Last-Event-ID: evt_k`, máy chủ tra cứu trong Ring Buffer.
+     + Chỉ phát lại các event có `ID &gt; evt_k` (ví dụ từ `evt_002` trở đi). Tuyệt đối không phát lại `evt_001` đã gửi thành công trước đó.
+     + Tiếp tục stream các chunk mới theo thời gian thực mà không làm lặp từ ngữ trên màn hình người dùng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Xây dựng đường truyền HTTP Streaming có khả năng tự phục hồi (Resilient Streaming) yêu cầu giải quyết đồng thời hai thách thức: Ngăn chặn timeout trung gian bằng Heartbeat Ping và đảm bảo ngữ nghĩa chính xác một lần (Exactly-Once Semantics) khi tái kết nối bằng con trỏ trạng thái `Last-Event-ID` kết hợp bộ nhớ đệm sự kiện phía máy chủ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+MDN Web Docs - Server-sent events: https://developer.mozilla.org/en-US/docs/Web/API/Server-sent_events và RFC 8895 (HTTP Last-Event-ID)</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1552,28 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Theo dõi state theo một chiều và tách retry của queue khỏi bảo đảm side effect.
-Phân tích theo nguyên lý thiết kế: Theo dõi state theo một chiều và tách retry của queue khỏi bảo đảm side effect.</t>
+- [1.0 điểm] Thiết kế State Machine nhất quán mà client quan sát được theo một chiều từ QUEUED -&gt; RUNNING -&gt; FAILED terminal.
+- [1.5 điểm] Xác định rõ trách nhiệm retry của Queue/System: xử lý transient errors, visibility timeout, DLQ và idempotent execution.
+- [1.5 điểm] Phân định rõ trách nhiệm của Client: dừng retry khi nhận terminal failure, chỉ retry khi có user action với Idempotency Key mới.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Theo dõi Máy trạng thái (State Machine) mà Client Quan sát được:
+   - Trạng thái 1: `QUEUED` - Yêu cầu được tiếp nhận vào hàng đợi, hệ thống trả về HTTP 202 Accepted kèm `job_id`.
+   - Trạng thái 2: `RUNNING` - Worker 1 lấy job và bắt đầu thực thi, phát heartbeat cập nhật trạng thái.
+   - Sự cố Worker 1 crash: Visibility timeout của hàng đợi hết hạn, job được tự động chuyển giao lại (redelivered). Client polling vẫn nhìn thấy trạng thái `RUNNING` (hoặc `RUNNING (Attempt 2)`), không bị chuyển ngược về trạng thái không hợp lệ.
+   - Trạng thái 3: `FAILED (Terminal)` - Worker 2 thử lại nhưng gặp lỗi không thể khắc phục hoặc vượt quá `max_retries = 3`. Trạng thái chuyển sang FAILED cuối cùng kèm `error_code` và thông điệp chi tiết.
+   - Nguyên tắc chuyển trạng thái: Phải bảo đảm tính đơn hướng (Monotonic Forward Progress) đối với client: `QUEUED -&gt; RUNNING -&gt; FAILED`.
+2. Phân định Ranh giới Trách nhiệm Retry (Retry Boundary &amp; Responsibilities):
+   - Trách nhiệm của Hàng đợi / Hệ thống (Infrastructure &amp; Queue Responsibility):
+     + Tự động retry đối với các lỗi tạm thời (Transient Failures): Worker crash đột ngột, mất kết nối mạng, container bị OOMKilled.
+     + Sử dụng cơ chế Visibility Timeout, Exponential Backoff và Dead-Letter Queue (DLQ) có giới hạn số lần thử lại tối đa.
+     + Bắt buộc các bước công việc phải có tính lũy kế (Idempotent Execution) để khi Worker 2 chạy lại không gây tác dụng phụ trùng lặp (ví dụ: không trừ tiền thẻ tín dụng 2 lần).
+   - Trách nhiệm của Client (Client Responsibility):
+     + Khi nhận trạng thái `FAILED (Terminal)`, client TUYỆT ĐỐI KHÔNG được tự động retry liên tục để tránh gây bão request (Thundering Herd Problem).
+     + Client chỉ được phép retry khi có hành động chủ động từ người dùng (User-Initiated Action) hoặc sau khi người dùng đã sửa đổi tham số đầu vào, đính kèm `Idempotency-Key` mới.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Quản trị trạng thái bất đồng bộ phân tán đòi hỏi sự phân định minh bạch giữa lỗi nhất thời của hạ tầng (Transient Infrastructure Errors) và lỗi vĩnh viễn của nghiệp vụ (Terminal Business Errors). Hệ thống hàng đợi chịu trách nhiệm retry nội bộ an toàn với tính lũy đẳng, trong khi client phải tôn trọng trạng thái Terminal để ngăn chặn vòng lặp retry vô tận làm tê liệt hệ thống.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Enterprise Integration Patterns - Idempotent Consumer &amp; AWS Architecture Guide for Asynchronous Messaging</t>
         </is>
       </c>
     </row>
@@ -1424,10 +1652,26 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Theo dõi nơi lưu message/status qua lần đổi replica; đừng dùng sticky session làm invariant.
-Phân tích theo nguyên lý thiết kế: Theo dõi nơi lưu message/status qua lần đổi replica; đừng dùng sticky session làm invariant.</t>
+- [1.0 điểm] Thiết kế kiến trúc Stateless Container hoàn chỉnh, bác bỏ sticky session và phân chia rõ ranh giới Messages vs Workflow Status.
+- [1.5 điểm] Mô tả chu trình đọc-xử lý-ghi atomic state với Redis và Persistent Database cho mỗi request độc lập.
+- [1.5 điểm] Xây dựng kịch bản kiểm thử Chaos Swapping đa replica chi tiết chứng minh tính toàn vẹn trạng thái khi thay thế container.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Ranh giới State và Ngoại biên hóa Dữ liệu (State Externalization):
+   - Tuân thủ nghiêm ngặt Factor VI (Processes are Stateless) của 12-Factor App: Tuyệt đối không lưu trữ tin nhắn hay trạng thái workflow trong RAM/Disk cục bộ của container, và KHÔNG dựa vào Sticky Session của bộ cân bằng tải.
+   - Phân chia hai ranh giới lưu trữ ngoại biên độc lập:
+     + `Conversation Messages Store` (PostgreSQL / DynamoDB): Lưu trữ toàn bộ lịch sử tin nhắn tuần tự, đảm bảo tính bền vững (durability) và toàn vẹn dữ liệu lâu dài.
+     + `Workflow Status &amp; Execution Context` (Redis Cluster / Distributed Key-Value): Lưu trữ trạng thái máy trạng thái hiện tại (`step_id`, `state_variables`, `execution_locks`) với cơ chế TTL và khóa phân tán (Distributed Locks).
+   - Chu trình xử lý mỗi Request độc lập:
+     Nhận `conversation_id` -&gt; Kéo state và 10 tin nhắn gần nhất từ Redis/DB -&gt; Xử lý logic agent -&gt; Ghi atomic commit cập nhật tin nhắn và status mới vào DB/Redis -&gt; Trả response.
+2. Thiết kế Bộ kiểm thử Thay thế Replica (Replica Chaos &amp; Swapping Test Suite):
+   - Bước 1 (Khởi tạo phiên trên Replica 1): Gửi Request 1 (`POST /chat`) tới Replica R1; tạo conversation C1, ghi tin nhắn M1, workflow status `awaiting_tool`. Xác nhận R1 ghi thành công vào DB và Redis.
+   - Bước 2 (Hủy diệt và Chuyển đổi Replica): Lập tức dừng tiến trình R1 (`docker stop R1`). Gửi tiếp Request 2 (`POST /chat` gửi tool output) qua Load Balancer; Load Balancer định tuyến tới Replica R2 hoàn toàn mới.
+   - Bước 3 (Kiểm tra Tính Toàn vẹn Context trên Replica 2): Khẳng định R2 truy vấn DB/Redis và tải đầy đủ ngữ cảnh tin nhắn M1 cùng trạng thái `awaiting_tool`, tiếp tục thực thi chuyển workflow sang `completed` và ghi nhận tin nhắn phản hồi M2.
+   - Bước 4 (Xác minh trên Replica 3): Gửi Request 3 tới Replica R3; xác nhận R3 trả về toàn bộ lịch sử [M1, M2] không bị mất mát hay suy thoái dữ liệu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong môi trường điện toán đám mây hiện đại, container có thể bị hủy diệt hoặc thay thế bất kỳ lúc nào do quá trình autoscaling, rolling deploy hoặc node failure. Bằng cách ngoại biên hóa toàn bộ trạng thái vào các hệ thống lưu trữ phân tán chuyên trách, kiến trúc bảo đảm bất kỳ replica nào cũng có thể phục vụ bất kỳ request nào mà không cần duy trì kết nối dính (Sticky Sessions).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+The Twelve-Factor App: Factor VI (Processes) &amp; Martin Kleppmann - Designing Data-Intensive Applications</t>
         </is>
       </c>
     </row>
